--- a/Overpotnital/O2/BOL/Edited/CN BM o2_edited.xlsx
+++ b/Overpotnital/O2/BOL/Edited/CN BM o2_edited.xlsx
@@ -612,10 +612,10 @@
         <f>A4*B4</f>
         <v/>
       </c>
-      <c r="D4" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E4" t="n">
+      <c r="D4" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F4" s="0">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="S4" s="0" t="n">
-        <v>-0.513</v>
+        <v>-0.517</v>
       </c>
     </row>
     <row r="5">
@@ -680,10 +680,10 @@
         <f>A5*B5</f>
         <v/>
       </c>
-      <c r="D5" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="D5" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E5" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F5" s="0">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="S5" s="0" t="n">
-        <v>-0.0351</v>
+        <v>-0.0358</v>
       </c>
       <c r="V5" s="0" t="inlineStr">
         <is>
@@ -758,10 +758,10 @@
         <f>A6*B6</f>
         <v/>
       </c>
-      <c r="D6" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D6" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E6" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F6" s="0">
@@ -825,10 +825,10 @@
         <f>A7*B7</f>
         <v/>
       </c>
-      <c r="D7" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E7" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F7" s="0">
@@ -892,10 +892,10 @@
         <f>A8*B8</f>
         <v/>
       </c>
-      <c r="D8" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F8" s="0">
@@ -959,10 +959,10 @@
         <f>A9*B9</f>
         <v/>
       </c>
-      <c r="D9" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E9" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F9" s="0">
@@ -1026,10 +1026,10 @@
         <f>A10*B10</f>
         <v/>
       </c>
-      <c r="D10" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="D10" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E10" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F10" s="0">
@@ -1093,10 +1093,10 @@
         <f>A11*B11</f>
         <v/>
       </c>
-      <c r="D11" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="D11" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E11" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F11" s="0">
@@ -1160,10 +1160,10 @@
         <f>A12*B12</f>
         <v/>
       </c>
-      <c r="D12" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E12" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F12" s="0">
@@ -1227,10 +1227,10 @@
         <f>A13*B13</f>
         <v/>
       </c>
-      <c r="D13" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F13" s="0">
@@ -1294,10 +1294,10 @@
         <f>A14*B14</f>
         <v/>
       </c>
-      <c r="D14" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E14" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F14" s="0">
@@ -1361,10 +1361,10 @@
         <f>A15*B15</f>
         <v/>
       </c>
-      <c r="D15" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E15" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F15" s="0">
@@ -1428,10 +1428,10 @@
         <f>A16*B16</f>
         <v/>
       </c>
-      <c r="D16" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E16" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F16" s="0">
@@ -1495,10 +1495,10 @@
         <f>A17*B17</f>
         <v/>
       </c>
-      <c r="D17" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="D17" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E17" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F17" s="0">
@@ -1562,10 +1562,10 @@
         <f>A18*B18</f>
         <v/>
       </c>
-      <c r="D18" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="D18" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E18" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F18" s="0">
@@ -1629,10 +1629,10 @@
         <f>A19*B19</f>
         <v/>
       </c>
-      <c r="D19" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="D19" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E19" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F19" s="0">
@@ -1696,10 +1696,10 @@
         <f>A20*B20</f>
         <v/>
       </c>
-      <c r="D20" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E20" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F20" s="0">
@@ -1763,10 +1763,10 @@
         <f>A21*B21</f>
         <v/>
       </c>
-      <c r="D21" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E21" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F21" s="0">
@@ -1830,10 +1830,10 @@
         <f>A22*B22</f>
         <v/>
       </c>
-      <c r="D22" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="D22" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E22" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F22" s="0">
@@ -1897,10 +1897,10 @@
         <f>A23*B23</f>
         <v/>
       </c>
-      <c r="D23" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="D23" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E23" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F23" s="0">
@@ -1964,10 +1964,10 @@
         <f>A24*B24</f>
         <v/>
       </c>
-      <c r="D24" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E24" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F24" s="0">
@@ -2031,10 +2031,10 @@
         <f>A25*B25</f>
         <v/>
       </c>
-      <c r="D25" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="D25" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E25" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F25" s="0">
@@ -2098,10 +2098,10 @@
         <f>A26*B26</f>
         <v/>
       </c>
-      <c r="D26" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="D26" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E26" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F26" s="0">
@@ -2165,10 +2165,10 @@
         <f>A27*B27</f>
         <v/>
       </c>
-      <c r="D27" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="D27" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E27" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F27" s="0">
@@ -2232,10 +2232,10 @@
         <f>A28*B28</f>
         <v/>
       </c>
-      <c r="D28" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="D28" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E28" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F28" s="0">
@@ -2299,10 +2299,10 @@
         <f>A29*B29</f>
         <v/>
       </c>
-      <c r="D29" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="D29" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E29" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F29" s="0">
@@ -2366,10 +2366,10 @@
         <f>A30*B30</f>
         <v/>
       </c>
-      <c r="D30" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E30" t="n">
+      <c r="D30" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E30" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F30" s="0">
@@ -2433,10 +2433,10 @@
         <f>A31*B31</f>
         <v/>
       </c>
-      <c r="D31" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E31" t="n">
+      <c r="D31" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E31" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F31" s="0">
@@ -2500,10 +2500,10 @@
         <f>A32*B32</f>
         <v/>
       </c>
-      <c r="D32" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="D32" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E32" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F32" s="0">
@@ -2567,10 +2567,10 @@
         <f>A33*B33</f>
         <v/>
       </c>
-      <c r="D33" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E33" t="n">
+      <c r="D33" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E33" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F33" s="0">
@@ -2634,10 +2634,10 @@
         <f>A34*B34</f>
         <v/>
       </c>
-      <c r="D34" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E34" t="n">
+      <c r="D34" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E34" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F34" s="0">
@@ -2701,10 +2701,10 @@
         <f>A35*B35</f>
         <v/>
       </c>
-      <c r="D35" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E35" t="n">
+      <c r="D35" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E35" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F35" s="0">
@@ -2768,10 +2768,10 @@
         <f>A36*B36</f>
         <v/>
       </c>
-      <c r="D36" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E36" t="n">
+      <c r="D36" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E36" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F36" s="0">
@@ -2835,10 +2835,10 @@
         <f>A37*B37</f>
         <v/>
       </c>
-      <c r="D37" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E37" t="n">
+      <c r="D37" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E37" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F37" s="0">
@@ -2902,10 +2902,10 @@
         <f>A38*B38</f>
         <v/>
       </c>
-      <c r="D38" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E38" t="n">
+      <c r="D38" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E38" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F38" s="0">
@@ -2969,10 +2969,10 @@
         <f>A39*B39</f>
         <v/>
       </c>
-      <c r="D39" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E39" t="n">
+      <c r="D39" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E39" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F39" s="0">
@@ -3036,10 +3036,10 @@
         <f>A40*B40</f>
         <v/>
       </c>
-      <c r="D40" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E40" t="n">
+      <c r="D40" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E40" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F40" s="0">
@@ -3103,10 +3103,10 @@
         <f>A41*B41</f>
         <v/>
       </c>
-      <c r="D41" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E41" t="n">
+      <c r="D41" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E41" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F41" s="0">
@@ -3170,10 +3170,10 @@
         <f>A42*B42</f>
         <v/>
       </c>
-      <c r="D42" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E42" t="n">
+      <c r="D42" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E42" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F42" s="0">
@@ -3237,10 +3237,10 @@
         <f>A43*B43</f>
         <v/>
       </c>
-      <c r="D43" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E43" t="n">
+      <c r="D43" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E43" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F43" s="0">
@@ -3304,10 +3304,10 @@
         <f>A44*B44</f>
         <v/>
       </c>
-      <c r="D44" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E44" t="n">
+      <c r="D44" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E44" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F44" s="0">
@@ -3371,10 +3371,10 @@
         <f>A45*B45</f>
         <v/>
       </c>
-      <c r="D45" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E45" t="n">
+      <c r="D45" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E45" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F45" s="0">
@@ -3438,10 +3438,10 @@
         <f>A46*B46</f>
         <v/>
       </c>
-      <c r="D46" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E46" t="n">
+      <c r="D46" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E46" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F46" s="0">
@@ -3505,10 +3505,10 @@
         <f>A47*B47</f>
         <v/>
       </c>
-      <c r="D47" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E47" t="n">
+      <c r="D47" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E47" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F47" s="0">
@@ -3572,10 +3572,10 @@
         <f>A48*B48</f>
         <v/>
       </c>
-      <c r="D48" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E48" t="n">
+      <c r="D48" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E48" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F48" s="0">
@@ -3639,10 +3639,10 @@
         <f>A49*B49</f>
         <v/>
       </c>
-      <c r="D49" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E49" t="n">
+      <c r="D49" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E49" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F49" s="0">
@@ -3706,10 +3706,10 @@
         <f>A50*B50</f>
         <v/>
       </c>
-      <c r="D50" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E50" t="n">
+      <c r="D50" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E50" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F50" s="0">
@@ -3773,10 +3773,10 @@
         <f>A51*B51</f>
         <v/>
       </c>
-      <c r="D51" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E51" t="n">
+      <c r="D51" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E51" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F51" s="0">
@@ -3840,10 +3840,10 @@
         <f>A52*B52</f>
         <v/>
       </c>
-      <c r="D52" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E52" t="n">
+      <c r="D52" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E52" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F52" s="0">
@@ -3907,10 +3907,10 @@
         <f>A53*B53</f>
         <v/>
       </c>
-      <c r="D53" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E53" t="n">
+      <c r="D53" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E53" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F53" s="0">
@@ -3974,10 +3974,10 @@
         <f>A54*B54</f>
         <v/>
       </c>
-      <c r="D54" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E54" t="n">
+      <c r="D54" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E54" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F54" s="0">
@@ -4041,10 +4041,10 @@
         <f>A55*B55</f>
         <v/>
       </c>
-      <c r="D55" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E55" t="n">
+      <c r="D55" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E55" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F55" s="0">
@@ -4108,10 +4108,10 @@
         <f>A56*B56</f>
         <v/>
       </c>
-      <c r="D56" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E56" t="n">
+      <c r="D56" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E56" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F56" s="0">
@@ -4175,10 +4175,10 @@
         <f>A57*B57</f>
         <v/>
       </c>
-      <c r="D57" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E57" t="n">
+      <c r="D57" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E57" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F57" s="0">
@@ -4242,10 +4242,10 @@
         <f>A58*B58</f>
         <v/>
       </c>
-      <c r="D58" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E58" t="n">
+      <c r="D58" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E58" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F58" s="0">
@@ -4309,10 +4309,10 @@
         <f>A59*B59</f>
         <v/>
       </c>
-      <c r="D59" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E59" t="n">
+      <c r="D59" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E59" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F59" s="0">
@@ -4376,10 +4376,10 @@
         <f>A60*B60</f>
         <v/>
       </c>
-      <c r="D60" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E60" t="n">
+      <c r="D60" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E60" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F60" s="0">
@@ -4443,10 +4443,10 @@
         <f>A61*B61</f>
         <v/>
       </c>
-      <c r="D61" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E61" t="n">
+      <c r="D61" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E61" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F61" s="0">
@@ -4510,10 +4510,10 @@
         <f>A62*B62</f>
         <v/>
       </c>
-      <c r="D62" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E62" t="n">
+      <c r="D62" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E62" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F62" s="0">
@@ -4577,10 +4577,10 @@
         <f>A63*B63</f>
         <v/>
       </c>
-      <c r="D63" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E63" t="n">
+      <c r="D63" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E63" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F63" s="0">
@@ -4644,10 +4644,10 @@
         <f>A64*B64</f>
         <v/>
       </c>
-      <c r="D64" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E64" t="n">
+      <c r="D64" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E64" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F64" s="0">
@@ -4711,10 +4711,10 @@
         <f>A65*B65</f>
         <v/>
       </c>
-      <c r="D65" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E65" t="n">
+      <c r="D65" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E65" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F65" s="0">
@@ -4778,10 +4778,10 @@
         <f>A66*B66</f>
         <v/>
       </c>
-      <c r="D66" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E66" t="n">
+      <c r="D66" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E66" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F66" s="0">
@@ -4845,10 +4845,10 @@
         <f>A67*B67</f>
         <v/>
       </c>
-      <c r="D67" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E67" t="n">
+      <c r="D67" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E67" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F67" s="0">
@@ -4912,10 +4912,10 @@
         <f>A68*B68</f>
         <v/>
       </c>
-      <c r="D68" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E68" t="n">
+      <c r="D68" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E68" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F68" s="0">
@@ -4979,10 +4979,10 @@
         <f>A69*B69</f>
         <v/>
       </c>
-      <c r="D69" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E69" t="n">
+      <c r="D69" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E69" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F69" s="0">
@@ -5046,10 +5046,10 @@
         <f>A70*B70</f>
         <v/>
       </c>
-      <c r="D70" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E70" t="n">
+      <c r="D70" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E70" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F70" s="0">
@@ -5113,10 +5113,10 @@
         <f>A71*B71</f>
         <v/>
       </c>
-      <c r="D71" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E71" t="n">
+      <c r="D71" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E71" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F71" s="0">
@@ -5180,10 +5180,10 @@
         <f>A72*B72</f>
         <v/>
       </c>
-      <c r="D72" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E72" t="n">
+      <c r="D72" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E72" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F72" s="0">
@@ -5247,10 +5247,10 @@
         <f>A73*B73</f>
         <v/>
       </c>
-      <c r="D73" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E73" t="n">
+      <c r="D73" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E73" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F73" s="0">
@@ -5314,10 +5314,10 @@
         <f>A74*B74</f>
         <v/>
       </c>
-      <c r="D74" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E74" t="n">
+      <c r="D74" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E74" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F74" s="0">
@@ -5381,10 +5381,10 @@
         <f>A75*B75</f>
         <v/>
       </c>
-      <c r="D75" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E75" t="n">
+      <c r="D75" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E75" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F75" s="0">
@@ -5448,10 +5448,10 @@
         <f>A76*B76</f>
         <v/>
       </c>
-      <c r="D76" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E76" t="n">
+      <c r="D76" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E76" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F76" s="0">
@@ -5515,10 +5515,10 @@
         <f>A77*B77</f>
         <v/>
       </c>
-      <c r="D77" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E77" t="n">
+      <c r="D77" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E77" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F77" s="0">
@@ -5582,10 +5582,10 @@
         <f>A78*B78</f>
         <v/>
       </c>
-      <c r="D78" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E78" t="n">
+      <c r="D78" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E78" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F78" s="0">
@@ -5649,10 +5649,10 @@
         <f>A79*B79</f>
         <v/>
       </c>
-      <c r="D79" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E79" t="n">
+      <c r="D79" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E79" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F79" s="0">
@@ -5716,10 +5716,10 @@
         <f>A80*B80</f>
         <v/>
       </c>
-      <c r="D80" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E80" t="n">
+      <c r="D80" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E80" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F80" s="0">
@@ -5783,10 +5783,10 @@
         <f>A81*B81</f>
         <v/>
       </c>
-      <c r="D81" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E81" t="n">
+      <c r="D81" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E81" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F81" s="0">
@@ -5850,10 +5850,10 @@
         <f>A82*B82</f>
         <v/>
       </c>
-      <c r="D82" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E82" t="n">
+      <c r="D82" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E82" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F82" s="0">
@@ -5917,10 +5917,10 @@
         <f>A83*B83</f>
         <v/>
       </c>
-      <c r="D83" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E83" t="n">
+      <c r="D83" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E83" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F83" s="0">
@@ -5984,10 +5984,10 @@
         <f>A84*B84</f>
         <v/>
       </c>
-      <c r="D84" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E84" t="n">
+      <c r="D84" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E84" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F84" s="0">
@@ -6051,10 +6051,10 @@
         <f>A85*B85</f>
         <v/>
       </c>
-      <c r="D85" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E85" t="n">
+      <c r="D85" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E85" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F85" s="0">
@@ -6118,10 +6118,10 @@
         <f>A86*B86</f>
         <v/>
       </c>
-      <c r="D86" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E86" t="n">
+      <c r="D86" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E86" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F86" s="0">
@@ -6185,10 +6185,10 @@
         <f>A87*B87</f>
         <v/>
       </c>
-      <c r="D87" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E87" t="n">
+      <c r="D87" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E87" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F87" s="0">
@@ -6252,10 +6252,10 @@
         <f>A88*B88</f>
         <v/>
       </c>
-      <c r="D88" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E88" t="n">
+      <c r="D88" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E88" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F88" s="0">
@@ -6319,10 +6319,10 @@
         <f>A89*B89</f>
         <v/>
       </c>
-      <c r="D89" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E89" t="n">
+      <c r="D89" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E89" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F89" s="0">
@@ -6386,10 +6386,10 @@
         <f>A90*B90</f>
         <v/>
       </c>
-      <c r="D90" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E90" t="n">
+      <c r="D90" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E90" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F90" s="0">
@@ -6453,10 +6453,10 @@
         <f>A91*B91</f>
         <v/>
       </c>
-      <c r="D91" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E91" t="n">
+      <c r="D91" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E91" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F91" s="0">
@@ -6520,10 +6520,10 @@
         <f>A92*B92</f>
         <v/>
       </c>
-      <c r="D92" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E92" t="n">
+      <c r="D92" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E92" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F92" s="0">
@@ -6587,10 +6587,10 @@
         <f>A93*B93</f>
         <v/>
       </c>
-      <c r="D93" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E93" t="n">
+      <c r="D93" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E93" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F93" s="0">
@@ -6654,10 +6654,10 @@
         <f>A94*B94</f>
         <v/>
       </c>
-      <c r="D94" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E94" t="n">
+      <c r="D94" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E94" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F94" s="0">
@@ -6721,10 +6721,10 @@
         <f>A95*B95</f>
         <v/>
       </c>
-      <c r="D95" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E95" t="n">
+      <c r="D95" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E95" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F95" s="0">
@@ -6788,10 +6788,10 @@
         <f>A96*B96</f>
         <v/>
       </c>
-      <c r="D96" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E96" t="n">
+      <c r="D96" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E96" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F96" s="0">
@@ -6855,10 +6855,10 @@
         <f>A97*B97</f>
         <v/>
       </c>
-      <c r="D97" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E97" t="n">
+      <c r="D97" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E97" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F97" s="0">
@@ -6922,10 +6922,10 @@
         <f>A98*B98</f>
         <v/>
       </c>
-      <c r="D98" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E98" t="n">
+      <c r="D98" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E98" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F98" s="0">
@@ -6989,10 +6989,10 @@
         <f>A99*B99</f>
         <v/>
       </c>
-      <c r="D99" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E99" t="n">
+      <c r="D99" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E99" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F99" s="0">
@@ -7056,10 +7056,10 @@
         <f>A100*B100</f>
         <v/>
       </c>
-      <c r="D100" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E100" t="n">
+      <c r="D100" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E100" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F100" s="0">
@@ -7123,10 +7123,10 @@
         <f>A101*B101</f>
         <v/>
       </c>
-      <c r="D101" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E101" t="n">
+      <c r="D101" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E101" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F101" s="0">
@@ -7190,10 +7190,10 @@
         <f>A102*B102</f>
         <v/>
       </c>
-      <c r="D102" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E102" t="n">
+      <c r="D102" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E102" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F102" s="0">
@@ -7257,10 +7257,10 @@
         <f>A103*B103</f>
         <v/>
       </c>
-      <c r="D103" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E103" t="n">
+      <c r="D103" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E103" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F103" s="0">
@@ -7324,10 +7324,10 @@
         <f>A104*B104</f>
         <v/>
       </c>
-      <c r="D104" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E104" t="n">
+      <c r="D104" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E104" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F104" s="0">
@@ -7391,10 +7391,10 @@
         <f>A105*B105</f>
         <v/>
       </c>
-      <c r="D105" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E105" t="n">
+      <c r="D105" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E105" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F105" s="0">
@@ -7458,10 +7458,10 @@
         <f>A106*B106</f>
         <v/>
       </c>
-      <c r="D106" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E106" t="n">
+      <c r="D106" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E106" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F106" s="0">
@@ -7525,10 +7525,10 @@
         <f>A107*B107</f>
         <v/>
       </c>
-      <c r="D107" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E107" t="n">
+      <c r="D107" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E107" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F107" s="0">
@@ -7592,10 +7592,10 @@
         <f>A108*B108</f>
         <v/>
       </c>
-      <c r="D108" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E108" t="n">
+      <c r="D108" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E108" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F108" s="0">
@@ -7659,10 +7659,10 @@
         <f>A109*B109</f>
         <v/>
       </c>
-      <c r="D109" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E109" t="n">
+      <c r="D109" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E109" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F109" s="0">
@@ -7726,10 +7726,10 @@
         <f>A110*B110</f>
         <v/>
       </c>
-      <c r="D110" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E110" t="n">
+      <c r="D110" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E110" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F110" s="0">
@@ -7793,10 +7793,10 @@
         <f>A111*B111</f>
         <v/>
       </c>
-      <c r="D111" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E111" t="n">
+      <c r="D111" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E111" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F111" s="0">
@@ -7860,10 +7860,10 @@
         <f>A112*B112</f>
         <v/>
       </c>
-      <c r="D112" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E112" t="n">
+      <c r="D112" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E112" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F112" s="0">
@@ -7927,10 +7927,10 @@
         <f>A113*B113</f>
         <v/>
       </c>
-      <c r="D113" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E113" t="n">
+      <c r="D113" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E113" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F113" s="0">
@@ -7994,10 +7994,10 @@
         <f>A114*B114</f>
         <v/>
       </c>
-      <c r="D114" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E114" t="n">
+      <c r="D114" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E114" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F114" s="0">
@@ -8061,10 +8061,10 @@
         <f>A115*B115</f>
         <v/>
       </c>
-      <c r="D115" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E115" t="n">
+      <c r="D115" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E115" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F115" s="0">
@@ -8128,10 +8128,10 @@
         <f>A116*B116</f>
         <v/>
       </c>
-      <c r="D116" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E116" t="n">
+      <c r="D116" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E116" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F116" s="0">
@@ -8195,10 +8195,10 @@
         <f>A117*B117</f>
         <v/>
       </c>
-      <c r="D117" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E117" t="n">
+      <c r="D117" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E117" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F117" s="0">
@@ -8262,10 +8262,10 @@
         <f>A118*B118</f>
         <v/>
       </c>
-      <c r="D118" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E118" t="n">
+      <c r="D118" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E118" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F118" s="0">
@@ -8329,10 +8329,10 @@
         <f>A119*B119</f>
         <v/>
       </c>
-      <c r="D119" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E119" t="n">
+      <c r="D119" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E119" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F119" s="0">
@@ -8396,10 +8396,10 @@
         <f>A120*B120</f>
         <v/>
       </c>
-      <c r="D120" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E120" t="n">
+      <c r="D120" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E120" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F120" s="0">
@@ -8463,10 +8463,10 @@
         <f>A121*B121</f>
         <v/>
       </c>
-      <c r="D121" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E121" t="n">
+      <c r="D121" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E121" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F121" s="0">
@@ -8530,10 +8530,10 @@
         <f>A122*B122</f>
         <v/>
       </c>
-      <c r="D122" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E122" t="n">
+      <c r="D122" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E122" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F122" s="0">
@@ -8597,10 +8597,10 @@
         <f>A123*B123</f>
         <v/>
       </c>
-      <c r="D123" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E123" t="n">
+      <c r="D123" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E123" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F123" s="0">
@@ -8664,10 +8664,10 @@
         <f>A124*B124</f>
         <v/>
       </c>
-      <c r="D124" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E124" t="n">
+      <c r="D124" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E124" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F124" s="0">
@@ -8731,10 +8731,10 @@
         <f>A125*B125</f>
         <v/>
       </c>
-      <c r="D125" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E125" t="n">
+      <c r="D125" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E125" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F125" s="0">
@@ -8798,10 +8798,10 @@
         <f>A126*B126</f>
         <v/>
       </c>
-      <c r="D126" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E126" t="n">
+      <c r="D126" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E126" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F126" s="0">
@@ -8865,10 +8865,10 @@
         <f>A127*B127</f>
         <v/>
       </c>
-      <c r="D127" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E127" t="n">
+      <c r="D127" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E127" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F127" s="0">
@@ -8932,10 +8932,10 @@
         <f>A128*B128</f>
         <v/>
       </c>
-      <c r="D128" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E128" t="n">
+      <c r="D128" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E128" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F128" s="0">
@@ -8999,10 +8999,10 @@
         <f>A129*B129</f>
         <v/>
       </c>
-      <c r="D129" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E129" t="n">
+      <c r="D129" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E129" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F129" s="0">
@@ -9066,10 +9066,10 @@
         <f>A130*B130</f>
         <v/>
       </c>
-      <c r="D130" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E130" t="n">
+      <c r="D130" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E130" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F130" s="0">
@@ -9133,10 +9133,10 @@
         <f>A131*B131</f>
         <v/>
       </c>
-      <c r="D131" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E131" t="n">
+      <c r="D131" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E131" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F131" s="0">
@@ -9200,10 +9200,10 @@
         <f>A132*B132</f>
         <v/>
       </c>
-      <c r="D132" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E132" t="n">
+      <c r="D132" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E132" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F132" s="0">
@@ -9267,10 +9267,10 @@
         <f>A133*B133</f>
         <v/>
       </c>
-      <c r="D133" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E133" t="n">
+      <c r="D133" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E133" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F133" s="0">
@@ -9334,10 +9334,10 @@
         <f>A134*B134</f>
         <v/>
       </c>
-      <c r="D134" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E134" t="n">
+      <c r="D134" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E134" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F134" s="0">
@@ -9401,10 +9401,10 @@
         <f>A135*B135</f>
         <v/>
       </c>
-      <c r="D135" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E135" t="n">
+      <c r="D135" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E135" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F135" s="0">
@@ -9468,10 +9468,10 @@
         <f>A136*B136</f>
         <v/>
       </c>
-      <c r="D136" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E136" t="n">
+      <c r="D136" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E136" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F136" s="0">
@@ -9535,10 +9535,10 @@
         <f>A137*B137</f>
         <v/>
       </c>
-      <c r="D137" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E137" t="n">
+      <c r="D137" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E137" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F137" s="0">
@@ -9602,10 +9602,10 @@
         <f>A138*B138</f>
         <v/>
       </c>
-      <c r="D138" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E138" t="n">
+      <c r="D138" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E138" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F138" s="0">
@@ -9669,10 +9669,10 @@
         <f>A139*B139</f>
         <v/>
       </c>
-      <c r="D139" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E139" t="n">
+      <c r="D139" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E139" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F139" s="0">
@@ -9736,10 +9736,10 @@
         <f>A140*B140</f>
         <v/>
       </c>
-      <c r="D140" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E140" t="n">
+      <c r="D140" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E140" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F140" s="0">
@@ -9803,10 +9803,10 @@
         <f>A141*B141</f>
         <v/>
       </c>
-      <c r="D141" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E141" t="n">
+      <c r="D141" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E141" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F141" s="0">
@@ -9870,10 +9870,10 @@
         <f>A142*B142</f>
         <v/>
       </c>
-      <c r="D142" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E142" t="n">
+      <c r="D142" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E142" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F142" s="0">
@@ -9937,10 +9937,10 @@
         <f>A143*B143</f>
         <v/>
       </c>
-      <c r="D143" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E143" t="n">
+      <c r="D143" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E143" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F143" s="0">
@@ -10004,10 +10004,10 @@
         <f>A144*B144</f>
         <v/>
       </c>
-      <c r="D144" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E144" t="n">
+      <c r="D144" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E144" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F144" s="0">
@@ -10071,10 +10071,10 @@
         <f>A145*B145</f>
         <v/>
       </c>
-      <c r="D145" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E145" t="n">
+      <c r="D145" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E145" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F145" s="0">
@@ -10138,10 +10138,10 @@
         <f>A146*B146</f>
         <v/>
       </c>
-      <c r="D146" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E146" t="n">
+      <c r="D146" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E146" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F146" s="0">
@@ -10205,10 +10205,10 @@
         <f>A147*B147</f>
         <v/>
       </c>
-      <c r="D147" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E147" t="n">
+      <c r="D147" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E147" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F147" s="0">
@@ -10272,10 +10272,10 @@
         <f>A148*B148</f>
         <v/>
       </c>
-      <c r="D148" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E148" t="n">
+      <c r="D148" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E148" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F148" s="0">
@@ -10339,10 +10339,10 @@
         <f>A149*B149</f>
         <v/>
       </c>
-      <c r="D149" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E149" t="n">
+      <c r="D149" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E149" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F149" s="0">
@@ -10406,10 +10406,10 @@
         <f>A150*B150</f>
         <v/>
       </c>
-      <c r="D150" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E150" t="n">
+      <c r="D150" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E150" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F150" s="0">
@@ -10473,10 +10473,10 @@
         <f>A151*B151</f>
         <v/>
       </c>
-      <c r="D151" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E151" t="n">
+      <c r="D151" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E151" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F151" s="0">
@@ -10540,10 +10540,10 @@
         <f>A152*B152</f>
         <v/>
       </c>
-      <c r="D152" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E152" t="n">
+      <c r="D152" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E152" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F152" s="0">
@@ -10607,10 +10607,10 @@
         <f>A153*B153</f>
         <v/>
       </c>
-      <c r="D153" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E153" t="n">
+      <c r="D153" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E153" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F153" s="0">
@@ -10674,10 +10674,10 @@
         <f>A154*B154</f>
         <v/>
       </c>
-      <c r="D154" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E154" t="n">
+      <c r="D154" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E154" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F154" s="0">
@@ -10741,10 +10741,10 @@
         <f>A155*B155</f>
         <v/>
       </c>
-      <c r="D155" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E155" t="n">
+      <c r="D155" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E155" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F155" s="0">
@@ -10808,10 +10808,10 @@
         <f>A156*B156</f>
         <v/>
       </c>
-      <c r="D156" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E156" t="n">
+      <c r="D156" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E156" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F156" s="0">
@@ -10875,10 +10875,10 @@
         <f>A157*B157</f>
         <v/>
       </c>
-      <c r="D157" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E157" t="n">
+      <c r="D157" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E157" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F157" s="0">
@@ -10942,10 +10942,10 @@
         <f>A158*B158</f>
         <v/>
       </c>
-      <c r="D158" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E158" t="n">
+      <c r="D158" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E158" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F158" s="0">
@@ -11009,10 +11009,10 @@
         <f>A159*B159</f>
         <v/>
       </c>
-      <c r="D159" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E159" t="n">
+      <c r="D159" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E159" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F159" s="0">
@@ -11076,10 +11076,10 @@
         <f>A160*B160</f>
         <v/>
       </c>
-      <c r="D160" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E160" t="n">
+      <c r="D160" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E160" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F160" s="0">
@@ -11143,10 +11143,10 @@
         <f>A161*B161</f>
         <v/>
       </c>
-      <c r="D161" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E161" t="n">
+      <c r="D161" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E161" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F161" s="0">
@@ -11210,10 +11210,10 @@
         <f>A162*B162</f>
         <v/>
       </c>
-      <c r="D162" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E162" t="n">
+      <c r="D162" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E162" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F162" s="0">
@@ -11277,10 +11277,10 @@
         <f>A163*B163</f>
         <v/>
       </c>
-      <c r="D163" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E163" t="n">
+      <c r="D163" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E163" s="0" t="n">
         <v>0.01413</v>
       </c>
       <c r="F163" s="0">
@@ -11338,10 +11338,10 @@
         <f>A164*B164</f>
         <v/>
       </c>
-      <c r="D164" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E164" t="n">
+      <c r="D164" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E164" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F164" s="0">
@@ -11399,10 +11399,10 @@
         <f>A165*B165</f>
         <v/>
       </c>
-      <c r="D165" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E165" t="n">
+      <c r="D165" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E165" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F165" s="0">
@@ -11460,10 +11460,10 @@
         <f>A166*B166</f>
         <v/>
       </c>
-      <c r="D166" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E166" t="n">
+      <c r="D166" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E166" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F166" s="0">
@@ -11521,10 +11521,10 @@
         <f>A167*B167</f>
         <v/>
       </c>
-      <c r="D167" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E167" t="n">
+      <c r="D167" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E167" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F167" s="0">
@@ -11582,10 +11582,10 @@
         <f>A168*B168</f>
         <v/>
       </c>
-      <c r="D168" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E168" t="n">
+      <c r="D168" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E168" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F168" s="0">
@@ -11643,10 +11643,10 @@
         <f>A169*B169</f>
         <v/>
       </c>
-      <c r="D169" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E169" t="n">
+      <c r="D169" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E169" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F169" s="0">
@@ -11704,10 +11704,10 @@
         <f>A170*B170</f>
         <v/>
       </c>
-      <c r="D170" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E170" t="n">
+      <c r="D170" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E170" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F170" s="0">
@@ -11765,10 +11765,10 @@
         <f>A171*B171</f>
         <v/>
       </c>
-      <c r="D171" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E171" t="n">
+      <c r="D171" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E171" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F171" s="0">
@@ -11826,10 +11826,10 @@
         <f>A172*B172</f>
         <v/>
       </c>
-      <c r="D172" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E172" t="n">
+      <c r="D172" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E172" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F172" s="0">
@@ -11887,10 +11887,10 @@
         <f>A173*B173</f>
         <v/>
       </c>
-      <c r="D173" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E173" t="n">
+      <c r="D173" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E173" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F173" s="0">
@@ -11948,10 +11948,10 @@
         <f>A174*B174</f>
         <v/>
       </c>
-      <c r="D174" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E174" t="n">
+      <c r="D174" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E174" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F174" s="0">
@@ -12009,10 +12009,10 @@
         <f>A175*B175</f>
         <v/>
       </c>
-      <c r="D175" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E175" t="n">
+      <c r="D175" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E175" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F175" s="0">
@@ -12070,10 +12070,10 @@
         <f>A176*B176</f>
         <v/>
       </c>
-      <c r="D176" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E176" t="n">
+      <c r="D176" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E176" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F176" s="0">
@@ -12131,10 +12131,10 @@
         <f>A177*B177</f>
         <v/>
       </c>
-      <c r="D177" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E177" t="n">
+      <c r="D177" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E177" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F177" s="0">
@@ -12192,10 +12192,10 @@
         <f>A178*B178</f>
         <v/>
       </c>
-      <c r="D178" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E178" t="n">
+      <c r="D178" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E178" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F178" s="0">
@@ -12253,10 +12253,10 @@
         <f>A179*B179</f>
         <v/>
       </c>
-      <c r="D179" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E179" t="n">
+      <c r="D179" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E179" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F179" s="0">
@@ -12314,10 +12314,10 @@
         <f>A180*B180</f>
         <v/>
       </c>
-      <c r="D180" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E180" t="n">
+      <c r="D180" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E180" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F180" s="0">
@@ -12375,10 +12375,10 @@
         <f>A181*B181</f>
         <v/>
       </c>
-      <c r="D181" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E181" t="n">
+      <c r="D181" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E181" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F181" s="0">
@@ -12436,10 +12436,10 @@
         <f>A182*B182</f>
         <v/>
       </c>
-      <c r="D182" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E182" t="n">
+      <c r="D182" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E182" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F182" s="0">
@@ -12497,10 +12497,10 @@
         <f>A183*B183</f>
         <v/>
       </c>
-      <c r="D183" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E183" t="n">
+      <c r="D183" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E183" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F183" s="0">
@@ -12558,10 +12558,10 @@
         <f>A184*B184</f>
         <v/>
       </c>
-      <c r="D184" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E184" t="n">
+      <c r="D184" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E184" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F184" s="0">
@@ -12619,10 +12619,10 @@
         <f>A185*B185</f>
         <v/>
       </c>
-      <c r="D185" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E185" t="n">
+      <c r="D185" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E185" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F185" s="0">
@@ -12680,10 +12680,10 @@
         <f>A186*B186</f>
         <v/>
       </c>
-      <c r="D186" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E186" t="n">
+      <c r="D186" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E186" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F186" s="0">
@@ -12741,10 +12741,10 @@
         <f>A187*B187</f>
         <v/>
       </c>
-      <c r="D187" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E187" t="n">
+      <c r="D187" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E187" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F187" s="0">
@@ -12802,10 +12802,10 @@
         <f>A188*B188</f>
         <v/>
       </c>
-      <c r="D188" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E188" t="n">
+      <c r="D188" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E188" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F188" s="0">
@@ -12863,10 +12863,10 @@
         <f>A189*B189</f>
         <v/>
       </c>
-      <c r="D189" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E189" t="n">
+      <c r="D189" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E189" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F189" s="0">
@@ -12924,10 +12924,10 @@
         <f>A190*B190</f>
         <v/>
       </c>
-      <c r="D190" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E190" t="n">
+      <c r="D190" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E190" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F190" s="0">
@@ -12985,10 +12985,10 @@
         <f>A191*B191</f>
         <v/>
       </c>
-      <c r="D191" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E191" t="n">
+      <c r="D191" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E191" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F191" s="0">
@@ -13046,10 +13046,10 @@
         <f>A192*B192</f>
         <v/>
       </c>
-      <c r="D192" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E192" t="n">
+      <c r="D192" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E192" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F192" s="0">
@@ -13107,10 +13107,10 @@
         <f>A193*B193</f>
         <v/>
       </c>
-      <c r="D193" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E193" t="n">
+      <c r="D193" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E193" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F193" s="0">
@@ -13168,10 +13168,10 @@
         <f>A194*B194</f>
         <v/>
       </c>
-      <c r="D194" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E194" t="n">
+      <c r="D194" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E194" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F194" s="0">
@@ -13229,10 +13229,10 @@
         <f>A195*B195</f>
         <v/>
       </c>
-      <c r="D195" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E195" t="n">
+      <c r="D195" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E195" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F195" s="0">
@@ -13290,10 +13290,10 @@
         <f>A196*B196</f>
         <v/>
       </c>
-      <c r="D196" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E196" t="n">
+      <c r="D196" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E196" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F196" s="0">
@@ -13351,10 +13351,10 @@
         <f>A197*B197</f>
         <v/>
       </c>
-      <c r="D197" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E197" t="n">
+      <c r="D197" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E197" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F197" s="0">
@@ -13412,10 +13412,10 @@
         <f>A198*B198</f>
         <v/>
       </c>
-      <c r="D198" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E198" t="n">
+      <c r="D198" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E198" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F198" s="0">
@@ -13473,10 +13473,10 @@
         <f>A199*B199</f>
         <v/>
       </c>
-      <c r="D199" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E199" t="n">
+      <c r="D199" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E199" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F199" s="0">
@@ -13534,10 +13534,10 @@
         <f>A200*B200</f>
         <v/>
       </c>
-      <c r="D200" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E200" t="n">
+      <c r="D200" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E200" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F200" s="0">
@@ -13595,10 +13595,10 @@
         <f>A201*B201</f>
         <v/>
       </c>
-      <c r="D201" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E201" t="n">
+      <c r="D201" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E201" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F201" s="0">
@@ -13656,10 +13656,10 @@
         <f>A202*B202</f>
         <v/>
       </c>
-      <c r="D202" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E202" t="n">
+      <c r="D202" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E202" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F202" s="0">
@@ -13717,10 +13717,10 @@
         <f>A203*B203</f>
         <v/>
       </c>
-      <c r="D203" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E203" t="n">
+      <c r="D203" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E203" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F203" s="0">
@@ -13778,10 +13778,10 @@
         <f>A204*B204</f>
         <v/>
       </c>
-      <c r="D204" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E204" t="n">
+      <c r="D204" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E204" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F204" s="0">
@@ -13839,10 +13839,10 @@
         <f>A205*B205</f>
         <v/>
       </c>
-      <c r="D205" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E205" t="n">
+      <c r="D205" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E205" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F205" s="0">
@@ -13900,10 +13900,10 @@
         <f>A206*B206</f>
         <v/>
       </c>
-      <c r="D206" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E206" t="n">
+      <c r="D206" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E206" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F206" s="0">
@@ -13961,10 +13961,10 @@
         <f>A207*B207</f>
         <v/>
       </c>
-      <c r="D207" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E207" t="n">
+      <c r="D207" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E207" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F207" s="0">
@@ -14022,10 +14022,10 @@
         <f>A208*B208</f>
         <v/>
       </c>
-      <c r="D208" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E208" t="n">
+      <c r="D208" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E208" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F208" s="0">
@@ -14083,10 +14083,10 @@
         <f>A209*B209</f>
         <v/>
       </c>
-      <c r="D209" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E209" t="n">
+      <c r="D209" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E209" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F209" s="0">
@@ -14144,10 +14144,10 @@
         <f>A210*B210</f>
         <v/>
       </c>
-      <c r="D210" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E210" t="n">
+      <c r="D210" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E210" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F210" s="0">
@@ -14205,10 +14205,10 @@
         <f>A211*B211</f>
         <v/>
       </c>
-      <c r="D211" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E211" t="n">
+      <c r="D211" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E211" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F211" s="0">
@@ -14266,10 +14266,10 @@
         <f>A212*B212</f>
         <v/>
       </c>
-      <c r="D212" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E212" t="n">
+      <c r="D212" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E212" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F212" s="0">
@@ -14327,10 +14327,10 @@
         <f>A213*B213</f>
         <v/>
       </c>
-      <c r="D213" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E213" t="n">
+      <c r="D213" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E213" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F213" s="0">
@@ -14388,10 +14388,10 @@
         <f>A214*B214</f>
         <v/>
       </c>
-      <c r="D214" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E214" t="n">
+      <c r="D214" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E214" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F214" s="0">
@@ -14449,10 +14449,10 @@
         <f>A215*B215</f>
         <v/>
       </c>
-      <c r="D215" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E215" t="n">
+      <c r="D215" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E215" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F215" s="0">
@@ -14510,10 +14510,10 @@
         <f>A216*B216</f>
         <v/>
       </c>
-      <c r="D216" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E216" t="n">
+      <c r="D216" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E216" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F216" s="0">
@@ -14571,10 +14571,10 @@
         <f>A217*B217</f>
         <v/>
       </c>
-      <c r="D217" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E217" t="n">
+      <c r="D217" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E217" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F217" s="0">
@@ -14632,10 +14632,10 @@
         <f>A218*B218</f>
         <v/>
       </c>
-      <c r="D218" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E218" t="n">
+      <c r="D218" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E218" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F218" s="0">
@@ -14693,10 +14693,10 @@
         <f>A219*B219</f>
         <v/>
       </c>
-      <c r="D219" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E219" t="n">
+      <c r="D219" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E219" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F219" s="0">
@@ -14754,10 +14754,10 @@
         <f>A220*B220</f>
         <v/>
       </c>
-      <c r="D220" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E220" t="n">
+      <c r="D220" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E220" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F220" s="0">
@@ -14815,10 +14815,10 @@
         <f>A221*B221</f>
         <v/>
       </c>
-      <c r="D221" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E221" t="n">
+      <c r="D221" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E221" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F221" s="0">
@@ -14876,10 +14876,10 @@
         <f>A222*B222</f>
         <v/>
       </c>
-      <c r="D222" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E222" t="n">
+      <c r="D222" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E222" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F222" s="0">
@@ -14937,10 +14937,10 @@
         <f>A223*B223</f>
         <v/>
       </c>
-      <c r="D223" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E223" t="n">
+      <c r="D223" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E223" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F223" s="0">
@@ -14998,10 +14998,10 @@
         <f>A224*B224</f>
         <v/>
       </c>
-      <c r="D224" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E224" t="n">
+      <c r="D224" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E224" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F224" s="0">
@@ -15059,10 +15059,10 @@
         <f>A225*B225</f>
         <v/>
       </c>
-      <c r="D225" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E225" t="n">
+      <c r="D225" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E225" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F225" s="0">
@@ -15124,10 +15124,10 @@
         <f>A226*B226</f>
         <v/>
       </c>
-      <c r="D226" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E226" t="n">
+      <c r="D226" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E226" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F226" s="0">
@@ -15185,10 +15185,10 @@
         <f>A227*B227</f>
         <v/>
       </c>
-      <c r="D227" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E227" t="n">
+      <c r="D227" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E227" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F227" s="0">
@@ -15246,10 +15246,10 @@
         <f>A228*B228</f>
         <v/>
       </c>
-      <c r="D228" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E228" t="n">
+      <c r="D228" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E228" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F228" s="0">
@@ -15307,10 +15307,10 @@
         <f>A229*B229</f>
         <v/>
       </c>
-      <c r="D229" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E229" t="n">
+      <c r="D229" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E229" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F229" s="0">
@@ -15368,10 +15368,10 @@
         <f>A230*B230</f>
         <v/>
       </c>
-      <c r="D230" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E230" t="n">
+      <c r="D230" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E230" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F230" s="0">
@@ -15429,10 +15429,10 @@
         <f>A231*B231</f>
         <v/>
       </c>
-      <c r="D231" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E231" t="n">
+      <c r="D231" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E231" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F231" s="0">
@@ -15490,10 +15490,10 @@
         <f>A232*B232</f>
         <v/>
       </c>
-      <c r="D232" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E232" t="n">
+      <c r="D232" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E232" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F232" s="0">
@@ -15551,10 +15551,10 @@
         <f>A233*B233</f>
         <v/>
       </c>
-      <c r="D233" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E233" t="n">
+      <c r="D233" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E233" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F233" s="0">
@@ -15612,10 +15612,10 @@
         <f>A234*B234</f>
         <v/>
       </c>
-      <c r="D234" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E234" t="n">
+      <c r="D234" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E234" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F234" s="0">
@@ -15673,10 +15673,10 @@
         <f>A235*B235</f>
         <v/>
       </c>
-      <c r="D235" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E235" t="n">
+      <c r="D235" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E235" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F235" s="0">
@@ -15734,10 +15734,10 @@
         <f>A236*B236</f>
         <v/>
       </c>
-      <c r="D236" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E236" t="n">
+      <c r="D236" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E236" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F236" s="0">
@@ -15795,10 +15795,10 @@
         <f>A237*B237</f>
         <v/>
       </c>
-      <c r="D237" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E237" t="n">
+      <c r="D237" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E237" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F237" s="0">
@@ -15856,10 +15856,10 @@
         <f>A238*B238</f>
         <v/>
       </c>
-      <c r="D238" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E238" t="n">
+      <c r="D238" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E238" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F238" s="0">
@@ -15917,10 +15917,10 @@
         <f>A239*B239</f>
         <v/>
       </c>
-      <c r="D239" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E239" t="n">
+      <c r="D239" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E239" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F239" s="0">
@@ -15978,10 +15978,10 @@
         <f>A240*B240</f>
         <v/>
       </c>
-      <c r="D240" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E240" t="n">
+      <c r="D240" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E240" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F240" s="0">
@@ -16039,10 +16039,10 @@
         <f>A241*B241</f>
         <v/>
       </c>
-      <c r="D241" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E241" t="n">
+      <c r="D241" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E241" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F241" s="0">
@@ -16100,10 +16100,10 @@
         <f>A242*B242</f>
         <v/>
       </c>
-      <c r="D242" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E242" t="n">
+      <c r="D242" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E242" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F242" s="0">
@@ -16161,10 +16161,10 @@
         <f>A243*B243</f>
         <v/>
       </c>
-      <c r="D243" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E243" t="n">
+      <c r="D243" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E243" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F243" s="0">
@@ -16222,10 +16222,10 @@
         <f>A244*B244</f>
         <v/>
       </c>
-      <c r="D244" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E244" t="n">
+      <c r="D244" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E244" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F244" s="0">
@@ -16283,10 +16283,10 @@
         <f>A245*B245</f>
         <v/>
       </c>
-      <c r="D245" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E245" t="n">
+      <c r="D245" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E245" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F245" s="0">
@@ -16344,10 +16344,10 @@
         <f>A246*B246</f>
         <v/>
       </c>
-      <c r="D246" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E246" t="n">
+      <c r="D246" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E246" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F246" s="0">
@@ -16405,10 +16405,10 @@
         <f>A247*B247</f>
         <v/>
       </c>
-      <c r="D247" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E247" t="n">
+      <c r="D247" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E247" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F247" s="0">
@@ -16466,10 +16466,10 @@
         <f>A248*B248</f>
         <v/>
       </c>
-      <c r="D248" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E248" t="n">
+      <c r="D248" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E248" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F248" s="0">
@@ -16527,10 +16527,10 @@
         <f>A249*B249</f>
         <v/>
       </c>
-      <c r="D249" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E249" t="n">
+      <c r="D249" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E249" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F249" s="0">
@@ -16588,10 +16588,10 @@
         <f>A250*B250</f>
         <v/>
       </c>
-      <c r="D250" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E250" t="n">
+      <c r="D250" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E250" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F250" s="0">
@@ -16649,10 +16649,10 @@
         <f>A251*B251</f>
         <v/>
       </c>
-      <c r="D251" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E251" t="n">
+      <c r="D251" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E251" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F251" s="0">
@@ -16710,10 +16710,10 @@
         <f>A252*B252</f>
         <v/>
       </c>
-      <c r="D252" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E252" t="n">
+      <c r="D252" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E252" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F252" s="0">
@@ -16771,10 +16771,10 @@
         <f>A253*B253</f>
         <v/>
       </c>
-      <c r="D253" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E253" t="n">
+      <c r="D253" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E253" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F253" s="0">
@@ -16832,10 +16832,10 @@
         <f>A254*B254</f>
         <v/>
       </c>
-      <c r="D254" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E254" t="n">
+      <c r="D254" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E254" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F254" s="0">
@@ -16893,10 +16893,10 @@
         <f>A255*B255</f>
         <v/>
       </c>
-      <c r="D255" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E255" t="n">
+      <c r="D255" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E255" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F255" s="0">
@@ -16954,10 +16954,10 @@
         <f>A256*B256</f>
         <v/>
       </c>
-      <c r="D256" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E256" t="n">
+      <c r="D256" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E256" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F256" s="0">
@@ -17015,10 +17015,10 @@
         <f>A257*B257</f>
         <v/>
       </c>
-      <c r="D257" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E257" t="n">
+      <c r="D257" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E257" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F257" s="0">
@@ -17076,10 +17076,10 @@
         <f>A258*B258</f>
         <v/>
       </c>
-      <c r="D258" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E258" t="n">
+      <c r="D258" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E258" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F258" s="0">
@@ -17137,10 +17137,10 @@
         <f>A259*B259</f>
         <v/>
       </c>
-      <c r="D259" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E259" t="n">
+      <c r="D259" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E259" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F259" s="0">
@@ -17198,10 +17198,10 @@
         <f>A260*B260</f>
         <v/>
       </c>
-      <c r="D260" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E260" t="n">
+      <c r="D260" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E260" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F260" s="0">
@@ -17259,10 +17259,10 @@
         <f>A261*B261</f>
         <v/>
       </c>
-      <c r="D261" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E261" t="n">
+      <c r="D261" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E261" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F261" s="0">
@@ -17320,10 +17320,10 @@
         <f>A262*B262</f>
         <v/>
       </c>
-      <c r="D262" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E262" t="n">
+      <c r="D262" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E262" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F262" s="0">
@@ -17381,10 +17381,10 @@
         <f>A263*B263</f>
         <v/>
       </c>
-      <c r="D263" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E263" t="n">
+      <c r="D263" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E263" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F263" s="0">
@@ -17442,10 +17442,10 @@
         <f>A264*B264</f>
         <v/>
       </c>
-      <c r="D264" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E264" t="n">
+      <c r="D264" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E264" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F264" s="0">
@@ -17503,10 +17503,10 @@
         <f>A265*B265</f>
         <v/>
       </c>
-      <c r="D265" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E265" t="n">
+      <c r="D265" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E265" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F265" s="0">
@@ -17564,10 +17564,10 @@
         <f>A266*B266</f>
         <v/>
       </c>
-      <c r="D266" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E266" t="n">
+      <c r="D266" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E266" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F266" s="0">
@@ -17625,10 +17625,10 @@
         <f>A267*B267</f>
         <v/>
       </c>
-      <c r="D267" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E267" t="n">
+      <c r="D267" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E267" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F267" s="0">
@@ -17686,10 +17686,10 @@
         <f>A268*B268</f>
         <v/>
       </c>
-      <c r="D268" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E268" t="n">
+      <c r="D268" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E268" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F268" s="0">
@@ -17747,10 +17747,10 @@
         <f>A269*B269</f>
         <v/>
       </c>
-      <c r="D269" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E269" t="n">
+      <c r="D269" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E269" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F269" s="0">
@@ -17808,10 +17808,10 @@
         <f>A270*B270</f>
         <v/>
       </c>
-      <c r="D270" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E270" t="n">
+      <c r="D270" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E270" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F270" s="0">
@@ -17869,10 +17869,10 @@
         <f>A271*B271</f>
         <v/>
       </c>
-      <c r="D271" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E271" t="n">
+      <c r="D271" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E271" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F271" s="0">
@@ -17930,10 +17930,10 @@
         <f>A272*B272</f>
         <v/>
       </c>
-      <c r="D272" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E272" t="n">
+      <c r="D272" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E272" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F272" s="0">
@@ -17991,10 +17991,10 @@
         <f>A273*B273</f>
         <v/>
       </c>
-      <c r="D273" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E273" t="n">
+      <c r="D273" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E273" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F273" s="0">
@@ -18052,10 +18052,10 @@
         <f>A274*B274</f>
         <v/>
       </c>
-      <c r="D274" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E274" t="n">
+      <c r="D274" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E274" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F274" s="0">
@@ -18113,10 +18113,10 @@
         <f>A275*B275</f>
         <v/>
       </c>
-      <c r="D275" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E275" t="n">
+      <c r="D275" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E275" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F275" s="0">
@@ -18174,10 +18174,10 @@
         <f>A276*B276</f>
         <v/>
       </c>
-      <c r="D276" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E276" t="n">
+      <c r="D276" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E276" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F276" s="0">
@@ -18235,10 +18235,10 @@
         <f>A277*B277</f>
         <v/>
       </c>
-      <c r="D277" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E277" t="n">
+      <c r="D277" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E277" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F277" s="0">
@@ -18296,10 +18296,10 @@
         <f>A278*B278</f>
         <v/>
       </c>
-      <c r="D278" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E278" t="n">
+      <c r="D278" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E278" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F278" s="0">
@@ -18357,10 +18357,10 @@
         <f>A279*B279</f>
         <v/>
       </c>
-      <c r="D279" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E279" t="n">
+      <c r="D279" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E279" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F279" s="0">
@@ -18418,10 +18418,10 @@
         <f>A280*B280</f>
         <v/>
       </c>
-      <c r="D280" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E280" t="n">
+      <c r="D280" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E280" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F280" s="0">
@@ -18479,10 +18479,10 @@
         <f>A281*B281</f>
         <v/>
       </c>
-      <c r="D281" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E281" t="n">
+      <c r="D281" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E281" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F281" s="0">
@@ -18540,10 +18540,10 @@
         <f>A282*B282</f>
         <v/>
       </c>
-      <c r="D282" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E282" t="n">
+      <c r="D282" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E282" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F282" s="0">
@@ -18601,10 +18601,10 @@
         <f>A283*B283</f>
         <v/>
       </c>
-      <c r="D283" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E283" t="n">
+      <c r="D283" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E283" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F283" s="0">
@@ -18662,10 +18662,10 @@
         <f>A284*B284</f>
         <v/>
       </c>
-      <c r="D284" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E284" t="n">
+      <c r="D284" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E284" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F284" s="0">
@@ -18723,10 +18723,10 @@
         <f>A285*B285</f>
         <v/>
       </c>
-      <c r="D285" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E285" t="n">
+      <c r="D285" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E285" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F285" s="0">
@@ -18784,10 +18784,10 @@
         <f>A286*B286</f>
         <v/>
       </c>
-      <c r="D286" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E286" t="n">
+      <c r="D286" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E286" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F286" s="0">
@@ -18845,10 +18845,10 @@
         <f>A287*B287</f>
         <v/>
       </c>
-      <c r="D287" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E287" t="n">
+      <c r="D287" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E287" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F287" s="0">
@@ -18906,10 +18906,10 @@
         <f>A288*B288</f>
         <v/>
       </c>
-      <c r="D288" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E288" t="n">
+      <c r="D288" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E288" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F288" s="0">
@@ -18967,10 +18967,10 @@
         <f>A289*B289</f>
         <v/>
       </c>
-      <c r="D289" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E289" t="n">
+      <c r="D289" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E289" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F289" s="0">
@@ -19028,10 +19028,10 @@
         <f>A290*B290</f>
         <v/>
       </c>
-      <c r="D290" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E290" t="n">
+      <c r="D290" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E290" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F290" s="0">
@@ -19089,10 +19089,10 @@
         <f>A291*B291</f>
         <v/>
       </c>
-      <c r="D291" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E291" t="n">
+      <c r="D291" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E291" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F291" s="0">
@@ -19150,10 +19150,10 @@
         <f>A292*B292</f>
         <v/>
       </c>
-      <c r="D292" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E292" t="n">
+      <c r="D292" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E292" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F292" s="0">
@@ -19211,10 +19211,10 @@
         <f>A293*B293</f>
         <v/>
       </c>
-      <c r="D293" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E293" t="n">
+      <c r="D293" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E293" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F293" s="0">
@@ -19272,10 +19272,10 @@
         <f>A294*B294</f>
         <v/>
       </c>
-      <c r="D294" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E294" t="n">
+      <c r="D294" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E294" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F294" s="0">
@@ -19333,10 +19333,10 @@
         <f>A295*B295</f>
         <v/>
       </c>
-      <c r="D295" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E295" t="n">
+      <c r="D295" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E295" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F295" s="0">
@@ -19394,10 +19394,10 @@
         <f>A296*B296</f>
         <v/>
       </c>
-      <c r="D296" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E296" t="n">
+      <c r="D296" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E296" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F296" s="0">
@@ -19455,10 +19455,10 @@
         <f>A297*B297</f>
         <v/>
       </c>
-      <c r="D297" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E297" t="n">
+      <c r="D297" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E297" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F297" s="0">
@@ -19516,10 +19516,10 @@
         <f>A298*B298</f>
         <v/>
       </c>
-      <c r="D298" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E298" t="n">
+      <c r="D298" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E298" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F298" s="0">
@@ -19577,10 +19577,10 @@
         <f>A299*B299</f>
         <v/>
       </c>
-      <c r="D299" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E299" t="n">
+      <c r="D299" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E299" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F299" s="0">
@@ -19638,10 +19638,10 @@
         <f>A300*B300</f>
         <v/>
       </c>
-      <c r="D300" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E300" t="n">
+      <c r="D300" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E300" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F300" s="0">
@@ -19699,10 +19699,10 @@
         <f>A301*B301</f>
         <v/>
       </c>
-      <c r="D301" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E301" t="n">
+      <c r="D301" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E301" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F301" s="0">
@@ -19760,10 +19760,10 @@
         <f>A302*B302</f>
         <v/>
       </c>
-      <c r="D302" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E302" t="n">
+      <c r="D302" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E302" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F302" s="0">
@@ -19821,10 +19821,10 @@
         <f>A303*B303</f>
         <v/>
       </c>
-      <c r="D303" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="E303" t="n">
+      <c r="D303" s="0" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="E303" s="0" t="n">
         <v>0.0141</v>
       </c>
       <c r="F303" s="0">
@@ -19945,7 +19945,7 @@
         <f>B2</f>
         <v/>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I2" s="0">
@@ -19972,7 +19972,7 @@
         <f>B3</f>
         <v/>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I3" s="0">
@@ -19999,7 +19999,7 @@
         <f>B4</f>
         <v/>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I4" s="0">
@@ -20026,7 +20026,7 @@
         <f>B5</f>
         <v/>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I5" s="0">
@@ -20053,7 +20053,7 @@
         <f>B6</f>
         <v/>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I6" s="0">
@@ -20080,7 +20080,7 @@
         <f>B7</f>
         <v/>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I7" s="0">
@@ -20107,7 +20107,7 @@
         <f>B8</f>
         <v/>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I8" s="0">
@@ -20134,7 +20134,7 @@
         <f>B9</f>
         <v/>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I9" s="0">
@@ -20161,7 +20161,7 @@
         <f>B10</f>
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I10" s="0">
@@ -20188,7 +20188,7 @@
         <f>B11</f>
         <v/>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I11" s="0">
@@ -20215,7 +20215,7 @@
         <f>B12</f>
         <v/>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I12" s="0">
@@ -20242,7 +20242,7 @@
         <f>B13</f>
         <v/>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I13" s="0">
@@ -20269,7 +20269,7 @@
         <f>B14</f>
         <v/>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I14" s="0">
@@ -20296,7 +20296,7 @@
         <f>B15</f>
         <v/>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I15" s="0">
@@ -20323,7 +20323,7 @@
         <f>B16</f>
         <v/>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I16" s="0">
@@ -20350,7 +20350,7 @@
         <f>B17</f>
         <v/>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I17" s="0">
@@ -20377,7 +20377,7 @@
         <f>B18</f>
         <v/>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I18" s="0">
@@ -20404,7 +20404,7 @@
         <f>B19</f>
         <v/>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I19" s="0">
@@ -20431,7 +20431,7 @@
         <f>B20</f>
         <v/>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I20" s="0">
@@ -20458,7 +20458,7 @@
         <f>B21</f>
         <v/>
       </c>
-      <c r="H21" t="n">
+      <c r="H21" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I21" s="0">
@@ -20485,7 +20485,7 @@
         <f>B22</f>
         <v/>
       </c>
-      <c r="H22" t="n">
+      <c r="H22" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I22" s="0">
@@ -20512,7 +20512,7 @@
         <f>B23</f>
         <v/>
       </c>
-      <c r="H23" t="n">
+      <c r="H23" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I23" s="0">
@@ -20539,7 +20539,7 @@
         <f>B24</f>
         <v/>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I24" s="0">
@@ -20566,7 +20566,7 @@
         <f>B25</f>
         <v/>
       </c>
-      <c r="H25" t="n">
+      <c r="H25" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I25" s="0">
@@ -20593,7 +20593,7 @@
         <f>B26</f>
         <v/>
       </c>
-      <c r="H26" t="n">
+      <c r="H26" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I26" s="0">
@@ -20620,7 +20620,7 @@
         <f>B27</f>
         <v/>
       </c>
-      <c r="H27" t="n">
+      <c r="H27" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I27" s="0">
@@ -20647,7 +20647,7 @@
         <f>B28</f>
         <v/>
       </c>
-      <c r="H28" t="n">
+      <c r="H28" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I28" s="0">
@@ -20674,7 +20674,7 @@
         <f>B29</f>
         <v/>
       </c>
-      <c r="H29" t="n">
+      <c r="H29" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I29" s="0">
@@ -20701,7 +20701,7 @@
         <f>B30</f>
         <v/>
       </c>
-      <c r="H30" t="n">
+      <c r="H30" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I30" s="0">
@@ -20728,7 +20728,7 @@
         <f>B31</f>
         <v/>
       </c>
-      <c r="H31" t="n">
+      <c r="H31" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I31" s="0">
@@ -20755,7 +20755,7 @@
         <f>B32</f>
         <v/>
       </c>
-      <c r="H32" t="n">
+      <c r="H32" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I32" s="0">
@@ -20782,7 +20782,7 @@
         <f>B33</f>
         <v/>
       </c>
-      <c r="H33" t="n">
+      <c r="H33" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I33" s="0">
@@ -20809,7 +20809,7 @@
         <f>B34</f>
         <v/>
       </c>
-      <c r="H34" t="n">
+      <c r="H34" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I34" s="0">
@@ -20836,7 +20836,7 @@
         <f>B35</f>
         <v/>
       </c>
-      <c r="H35" t="n">
+      <c r="H35" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I35" s="0">
@@ -20863,7 +20863,7 @@
         <f>B36</f>
         <v/>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I36" s="0">
@@ -20890,7 +20890,7 @@
         <f>B37</f>
         <v/>
       </c>
-      <c r="H37" t="n">
+      <c r="H37" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I37" s="0">
@@ -20917,7 +20917,7 @@
         <f>B38</f>
         <v/>
       </c>
-      <c r="H38" t="n">
+      <c r="H38" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I38" s="0">
@@ -20944,7 +20944,7 @@
         <f>B39</f>
         <v/>
       </c>
-      <c r="H39" t="n">
+      <c r="H39" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I39" s="0">
@@ -20971,7 +20971,7 @@
         <f>B40</f>
         <v/>
       </c>
-      <c r="H40" t="n">
+      <c r="H40" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I40" s="0">
@@ -20998,7 +20998,7 @@
         <f>B41</f>
         <v/>
       </c>
-      <c r="H41" t="n">
+      <c r="H41" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I41" s="0">
@@ -21025,7 +21025,7 @@
         <f>B42</f>
         <v/>
       </c>
-      <c r="H42" t="n">
+      <c r="H42" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I42" s="0">
@@ -21052,7 +21052,7 @@
         <f>B43</f>
         <v/>
       </c>
-      <c r="H43" t="n">
+      <c r="H43" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I43" s="0">
@@ -21079,7 +21079,7 @@
         <f>B44</f>
         <v/>
       </c>
-      <c r="H44" t="n">
+      <c r="H44" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I44" s="0">
@@ -21106,7 +21106,7 @@
         <f>B45</f>
         <v/>
       </c>
-      <c r="H45" t="n">
+      <c r="H45" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I45" s="0">
@@ -21133,7 +21133,7 @@
         <f>B46</f>
         <v/>
       </c>
-      <c r="H46" t="n">
+      <c r="H46" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I46" s="0">
@@ -21160,7 +21160,7 @@
         <f>B47</f>
         <v/>
       </c>
-      <c r="H47" t="n">
+      <c r="H47" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I47" s="0">
@@ -21187,7 +21187,7 @@
         <f>B48</f>
         <v/>
       </c>
-      <c r="H48" t="n">
+      <c r="H48" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I48" s="0">
@@ -21214,7 +21214,7 @@
         <f>B49</f>
         <v/>
       </c>
-      <c r="H49" t="n">
+      <c r="H49" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I49" s="0">
@@ -21241,7 +21241,7 @@
         <f>B50</f>
         <v/>
       </c>
-      <c r="H50" t="n">
+      <c r="H50" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I50" s="0">
@@ -21268,7 +21268,7 @@
         <f>B51</f>
         <v/>
       </c>
-      <c r="H51" t="n">
+      <c r="H51" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I51" s="0">
@@ -21295,7 +21295,7 @@
         <f>B52</f>
         <v/>
       </c>
-      <c r="H52" t="n">
+      <c r="H52" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I52" s="0">
@@ -21322,7 +21322,7 @@
         <f>B53</f>
         <v/>
       </c>
-      <c r="H53" t="n">
+      <c r="H53" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I53" s="0">
@@ -21349,7 +21349,7 @@
         <f>B54</f>
         <v/>
       </c>
-      <c r="H54" t="n">
+      <c r="H54" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I54" s="0">
@@ -21376,7 +21376,7 @@
         <f>B55</f>
         <v/>
       </c>
-      <c r="H55" t="n">
+      <c r="H55" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I55" s="0">
@@ -21403,7 +21403,7 @@
         <f>B56</f>
         <v/>
       </c>
-      <c r="H56" t="n">
+      <c r="H56" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I56" s="0">
@@ -21430,7 +21430,7 @@
         <f>B57</f>
         <v/>
       </c>
-      <c r="H57" t="n">
+      <c r="H57" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I57" s="0">
@@ -21457,7 +21457,7 @@
         <f>B58</f>
         <v/>
       </c>
-      <c r="H58" t="n">
+      <c r="H58" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I58" s="0">
@@ -21484,7 +21484,7 @@
         <f>B59</f>
         <v/>
       </c>
-      <c r="H59" t="n">
+      <c r="H59" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I59" s="0">
@@ -21511,7 +21511,7 @@
         <f>B60</f>
         <v/>
       </c>
-      <c r="H60" t="n">
+      <c r="H60" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I60" s="0">
@@ -21538,7 +21538,7 @@
         <f>B61</f>
         <v/>
       </c>
-      <c r="H61" t="n">
+      <c r="H61" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I61" s="0">
@@ -21565,7 +21565,7 @@
         <f>B62</f>
         <v/>
       </c>
-      <c r="H62" t="n">
+      <c r="H62" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I62" s="0">
@@ -21592,7 +21592,7 @@
         <f>B63</f>
         <v/>
       </c>
-      <c r="H63" t="n">
+      <c r="H63" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I63" s="0">
@@ -21619,7 +21619,7 @@
         <f>B64</f>
         <v/>
       </c>
-      <c r="H64" t="n">
+      <c r="H64" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I64" s="0">
@@ -21646,7 +21646,7 @@
         <f>B65</f>
         <v/>
       </c>
-      <c r="H65" t="n">
+      <c r="H65" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I65" s="0">
@@ -21673,7 +21673,7 @@
         <f>B66</f>
         <v/>
       </c>
-      <c r="H66" t="n">
+      <c r="H66" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I66" s="0">
@@ -21700,7 +21700,7 @@
         <f>B67</f>
         <v/>
       </c>
-      <c r="H67" t="n">
+      <c r="H67" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I67" s="0">
@@ -21727,7 +21727,7 @@
         <f>B68</f>
         <v/>
       </c>
-      <c r="H68" t="n">
+      <c r="H68" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I68" s="0">
@@ -21754,7 +21754,7 @@
         <f>B69</f>
         <v/>
       </c>
-      <c r="H69" t="n">
+      <c r="H69" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I69" s="0">
@@ -21781,7 +21781,7 @@
         <f>B70</f>
         <v/>
       </c>
-      <c r="H70" t="n">
+      <c r="H70" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I70" s="0">
@@ -21808,7 +21808,7 @@
         <f>B71</f>
         <v/>
       </c>
-      <c r="H71" t="n">
+      <c r="H71" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I71" s="0">
@@ -21835,7 +21835,7 @@
         <f>B72</f>
         <v/>
       </c>
-      <c r="H72" t="n">
+      <c r="H72" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I72" s="0">
@@ -21862,7 +21862,7 @@
         <f>B73</f>
         <v/>
       </c>
-      <c r="H73" t="n">
+      <c r="H73" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I73" s="0">
@@ -21889,7 +21889,7 @@
         <f>B74</f>
         <v/>
       </c>
-      <c r="H74" t="n">
+      <c r="H74" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I74" s="0">
@@ -21916,7 +21916,7 @@
         <f>B75</f>
         <v/>
       </c>
-      <c r="H75" t="n">
+      <c r="H75" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I75" s="0">
@@ -21943,7 +21943,7 @@
         <f>B76</f>
         <v/>
       </c>
-      <c r="H76" t="n">
+      <c r="H76" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I76" s="0">
@@ -21970,7 +21970,7 @@
         <f>B77</f>
         <v/>
       </c>
-      <c r="H77" t="n">
+      <c r="H77" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I77" s="0">
@@ -21997,7 +21997,7 @@
         <f>B78</f>
         <v/>
       </c>
-      <c r="H78" t="n">
+      <c r="H78" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I78" s="0">
@@ -22024,7 +22024,7 @@
         <f>B79</f>
         <v/>
       </c>
-      <c r="H79" t="n">
+      <c r="H79" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I79" s="0">
@@ -22051,7 +22051,7 @@
         <f>B80</f>
         <v/>
       </c>
-      <c r="H80" t="n">
+      <c r="H80" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I80" s="0">
@@ -22078,7 +22078,7 @@
         <f>B81</f>
         <v/>
       </c>
-      <c r="H81" t="n">
+      <c r="H81" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I81" s="0">
@@ -22105,7 +22105,7 @@
         <f>B82</f>
         <v/>
       </c>
-      <c r="H82" t="n">
+      <c r="H82" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I82" s="0">
@@ -22132,7 +22132,7 @@
         <f>B83</f>
         <v/>
       </c>
-      <c r="H83" t="n">
+      <c r="H83" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I83" s="0">
@@ -22159,7 +22159,7 @@
         <f>B84</f>
         <v/>
       </c>
-      <c r="H84" t="n">
+      <c r="H84" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I84" s="0">
@@ -22186,7 +22186,7 @@
         <f>B85</f>
         <v/>
       </c>
-      <c r="H85" t="n">
+      <c r="H85" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I85" s="0">
@@ -22213,7 +22213,7 @@
         <f>B86</f>
         <v/>
       </c>
-      <c r="H86" t="n">
+      <c r="H86" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I86" s="0">
@@ -22240,7 +22240,7 @@
         <f>B87</f>
         <v/>
       </c>
-      <c r="H87" t="n">
+      <c r="H87" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I87" s="0">
@@ -22267,7 +22267,7 @@
         <f>B88</f>
         <v/>
       </c>
-      <c r="H88" t="n">
+      <c r="H88" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I88" s="0">
@@ -22294,7 +22294,7 @@
         <f>B89</f>
         <v/>
       </c>
-      <c r="H89" t="n">
+      <c r="H89" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I89" s="0">
@@ -22321,7 +22321,7 @@
         <f>B90</f>
         <v/>
       </c>
-      <c r="H90" t="n">
+      <c r="H90" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I90" s="0">
@@ -22348,7 +22348,7 @@
         <f>B91</f>
         <v/>
       </c>
-      <c r="H91" t="n">
+      <c r="H91" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I91" s="0">
@@ -22375,7 +22375,7 @@
         <f>B92</f>
         <v/>
       </c>
-      <c r="H92" t="n">
+      <c r="H92" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I92" s="0">
@@ -22402,7 +22402,7 @@
         <f>B93</f>
         <v/>
       </c>
-      <c r="H93" t="n">
+      <c r="H93" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I93" s="0">
@@ -22429,7 +22429,7 @@
         <f>B94</f>
         <v/>
       </c>
-      <c r="H94" t="n">
+      <c r="H94" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I94" s="0">
@@ -22456,7 +22456,7 @@
         <f>B95</f>
         <v/>
       </c>
-      <c r="H95" t="n">
+      <c r="H95" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I95" s="0">
@@ -22483,7 +22483,7 @@
         <f>B96</f>
         <v/>
       </c>
-      <c r="H96" t="n">
+      <c r="H96" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I96" s="0">
@@ -22510,7 +22510,7 @@
         <f>B97</f>
         <v/>
       </c>
-      <c r="H97" t="n">
+      <c r="H97" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I97" s="0">
@@ -22537,7 +22537,7 @@
         <f>B98</f>
         <v/>
       </c>
-      <c r="H98" t="n">
+      <c r="H98" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I98" s="0">
@@ -22564,7 +22564,7 @@
         <f>B99</f>
         <v/>
       </c>
-      <c r="H99" t="n">
+      <c r="H99" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I99" s="0">
@@ -22591,7 +22591,7 @@
         <f>B100</f>
         <v/>
       </c>
-      <c r="H100" t="n">
+      <c r="H100" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I100" s="0">
@@ -22618,7 +22618,7 @@
         <f>B101</f>
         <v/>
       </c>
-      <c r="H101" t="n">
+      <c r="H101" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I101" s="0">
@@ -22645,7 +22645,7 @@
         <f>B102</f>
         <v/>
       </c>
-      <c r="H102" t="n">
+      <c r="H102" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I102" s="0">
@@ -22672,7 +22672,7 @@
         <f>B103</f>
         <v/>
       </c>
-      <c r="H103" t="n">
+      <c r="H103" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I103" s="0">
@@ -22699,7 +22699,7 @@
         <f>B104</f>
         <v/>
       </c>
-      <c r="H104" t="n">
+      <c r="H104" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I104" s="0">
@@ -22726,7 +22726,7 @@
         <f>B105</f>
         <v/>
       </c>
-      <c r="H105" t="n">
+      <c r="H105" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I105" s="0">
@@ -22753,7 +22753,7 @@
         <f>B106</f>
         <v/>
       </c>
-      <c r="H106" t="n">
+      <c r="H106" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I106" s="0">
@@ -22780,7 +22780,7 @@
         <f>B107</f>
         <v/>
       </c>
-      <c r="H107" t="n">
+      <c r="H107" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I107" s="0">
@@ -22807,7 +22807,7 @@
         <f>B108</f>
         <v/>
       </c>
-      <c r="H108" t="n">
+      <c r="H108" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I108" s="0">
@@ -22834,7 +22834,7 @@
         <f>B109</f>
         <v/>
       </c>
-      <c r="H109" t="n">
+      <c r="H109" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I109" s="0">
@@ -22861,7 +22861,7 @@
         <f>B110</f>
         <v/>
       </c>
-      <c r="H110" t="n">
+      <c r="H110" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I110" s="0">
@@ -22888,7 +22888,7 @@
         <f>B111</f>
         <v/>
       </c>
-      <c r="H111" t="n">
+      <c r="H111" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I111" s="0">
@@ -22915,7 +22915,7 @@
         <f>B112</f>
         <v/>
       </c>
-      <c r="H112" t="n">
+      <c r="H112" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I112" s="0">
@@ -22942,7 +22942,7 @@
         <f>B113</f>
         <v/>
       </c>
-      <c r="H113" t="n">
+      <c r="H113" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I113" s="0">
@@ -22969,7 +22969,7 @@
         <f>B114</f>
         <v/>
       </c>
-      <c r="H114" t="n">
+      <c r="H114" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I114" s="0">
@@ -22996,7 +22996,7 @@
         <f>B115</f>
         <v/>
       </c>
-      <c r="H115" t="n">
+      <c r="H115" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I115" s="0">
@@ -23023,7 +23023,7 @@
         <f>B116</f>
         <v/>
       </c>
-      <c r="H116" t="n">
+      <c r="H116" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I116" s="0">
@@ -23050,7 +23050,7 @@
         <f>B117</f>
         <v/>
       </c>
-      <c r="H117" t="n">
+      <c r="H117" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I117" s="0">
@@ -23077,7 +23077,7 @@
         <f>B118</f>
         <v/>
       </c>
-      <c r="H118" t="n">
+      <c r="H118" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I118" s="0">
@@ -23104,7 +23104,7 @@
         <f>B119</f>
         <v/>
       </c>
-      <c r="H119" t="n">
+      <c r="H119" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I119" s="0">
@@ -23131,7 +23131,7 @@
         <f>B120</f>
         <v/>
       </c>
-      <c r="H120" t="n">
+      <c r="H120" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I120" s="0">
@@ -23158,7 +23158,7 @@
         <f>B121</f>
         <v/>
       </c>
-      <c r="H121" t="n">
+      <c r="H121" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I121" s="0">
@@ -23185,7 +23185,7 @@
         <f>B122</f>
         <v/>
       </c>
-      <c r="H122" t="n">
+      <c r="H122" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I122" s="0">
@@ -23212,7 +23212,7 @@
         <f>B123</f>
         <v/>
       </c>
-      <c r="H123" t="n">
+      <c r="H123" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I123" s="0">
@@ -23239,7 +23239,7 @@
         <f>B124</f>
         <v/>
       </c>
-      <c r="H124" t="n">
+      <c r="H124" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I124" s="0">
@@ -23266,7 +23266,7 @@
         <f>B125</f>
         <v/>
       </c>
-      <c r="H125" t="n">
+      <c r="H125" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I125" s="0">
@@ -23293,7 +23293,7 @@
         <f>B126</f>
         <v/>
       </c>
-      <c r="H126" t="n">
+      <c r="H126" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I126" s="0">
@@ -23320,7 +23320,7 @@
         <f>B127</f>
         <v/>
       </c>
-      <c r="H127" t="n">
+      <c r="H127" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I127" s="0">
@@ -23347,7 +23347,7 @@
         <f>B128</f>
         <v/>
       </c>
-      <c r="H128" t="n">
+      <c r="H128" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I128" s="0">
@@ -23374,7 +23374,7 @@
         <f>B129</f>
         <v/>
       </c>
-      <c r="H129" t="n">
+      <c r="H129" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I129" s="0">
@@ -23401,7 +23401,7 @@
         <f>B130</f>
         <v/>
       </c>
-      <c r="H130" t="n">
+      <c r="H130" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I130" s="0">
@@ -23428,7 +23428,7 @@
         <f>B131</f>
         <v/>
       </c>
-      <c r="H131" t="n">
+      <c r="H131" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I131" s="0">
@@ -23455,7 +23455,7 @@
         <f>B132</f>
         <v/>
       </c>
-      <c r="H132" t="n">
+      <c r="H132" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I132" s="0">
@@ -23482,7 +23482,7 @@
         <f>B133</f>
         <v/>
       </c>
-      <c r="H133" t="n">
+      <c r="H133" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I133" s="0">
@@ -23495,7 +23495,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="0" t="n">
         <v>1391.38212</v>
       </c>
       <c r="B134" s="0" t="n">
@@ -23509,7 +23509,7 @@
         <f>B134</f>
         <v/>
       </c>
-      <c r="H134" t="n">
+      <c r="H134" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I134" s="0">
@@ -23522,7 +23522,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="0" t="n">
         <v>1401.66768</v>
       </c>
       <c r="B135" s="0" t="n">
@@ -23536,7 +23536,7 @@
         <f>B135</f>
         <v/>
       </c>
-      <c r="H135" t="n">
+      <c r="H135" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I135" s="0">
@@ -23549,7 +23549,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="0" t="n">
         <v>1412.15684</v>
       </c>
       <c r="B136" s="0" t="n">
@@ -23563,7 +23563,7 @@
         <f>B136</f>
         <v/>
       </c>
-      <c r="H136" t="n">
+      <c r="H136" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I136" s="0">
@@ -23576,7 +23576,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="0" t="n">
         <v>1422.23868</v>
       </c>
       <c r="B137" s="0" t="n">
@@ -23590,7 +23590,7 @@
         <f>B137</f>
         <v/>
       </c>
-      <c r="H137" t="n">
+      <c r="H137" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I137" s="0">
@@ -23603,7 +23603,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="0" t="n">
         <v>1432.72774</v>
       </c>
       <c r="B138" s="0" t="n">
@@ -23617,7 +23617,7 @@
         <f>B138</f>
         <v/>
       </c>
-      <c r="H138" t="n">
+      <c r="H138" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I138" s="0">
@@ -23630,7 +23630,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="0" t="n">
         <v>1443.4206</v>
       </c>
       <c r="B139" s="0" t="n">
@@ -23644,7 +23644,7 @@
         <f>B139</f>
         <v/>
       </c>
-      <c r="H139" t="n">
+      <c r="H139" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I139" s="0">
@@ -23657,7 +23657,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="0" t="n">
         <v>1453.70616</v>
       </c>
       <c r="B140" s="0" t="n">
@@ -23671,7 +23671,7 @@
         <f>B140</f>
         <v/>
       </c>
-      <c r="H140" t="n">
+      <c r="H140" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I140" s="0">
@@ -23684,7 +23684,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="0" t="n">
         <v>1464.29726</v>
       </c>
       <c r="B141" s="0" t="n">
@@ -23698,7 +23698,7 @@
         <f>B141</f>
         <v/>
       </c>
-      <c r="H141" t="n">
+      <c r="H141" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I141" s="0">
@@ -23725,7 +23725,7 @@
         <f>B142</f>
         <v/>
       </c>
-      <c r="H142" t="n">
+      <c r="H142" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I142" s="0">
@@ -23752,7 +23752,7 @@
         <f>B143</f>
         <v/>
       </c>
-      <c r="H143" t="n">
+      <c r="H143" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I143" s="0">
@@ -23779,7 +23779,7 @@
         <f>B144</f>
         <v/>
       </c>
-      <c r="H144" t="n">
+      <c r="H144" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I144" s="0">
@@ -23806,7 +23806,7 @@
         <f>B145</f>
         <v/>
       </c>
-      <c r="H145" t="n">
+      <c r="H145" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I145" s="0">
@@ -23833,7 +23833,7 @@
         <f>B146</f>
         <v/>
       </c>
-      <c r="H146" t="n">
+      <c r="H146" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I146" s="0">
@@ -23860,7 +23860,7 @@
         <f>B147</f>
         <v/>
       </c>
-      <c r="H147" t="n">
+      <c r="H147" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I147" s="0">
@@ -23887,7 +23887,7 @@
         <f>B148</f>
         <v/>
       </c>
-      <c r="H148" t="n">
+      <c r="H148" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I148" s="0">
@@ -23914,7 +23914,7 @@
         <f>B149</f>
         <v/>
       </c>
-      <c r="H149" t="n">
+      <c r="H149" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I149" s="0">
@@ -23941,7 +23941,7 @@
         <f>B150</f>
         <v/>
       </c>
-      <c r="H150" t="n">
+      <c r="H150" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I150" s="0">
@@ -23968,7 +23968,7 @@
         <f>B151</f>
         <v/>
       </c>
-      <c r="H151" t="n">
+      <c r="H151" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I151" s="0">
@@ -23995,7 +23995,7 @@
         <f>B152</f>
         <v/>
       </c>
-      <c r="H152" t="n">
+      <c r="H152" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I152" s="0">
@@ -24022,7 +24022,7 @@
         <f>B153</f>
         <v/>
       </c>
-      <c r="H153" t="n">
+      <c r="H153" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I153" s="0">
@@ -24049,7 +24049,7 @@
         <f>B154</f>
         <v/>
       </c>
-      <c r="H154" t="n">
+      <c r="H154" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I154" s="0">
@@ -24076,7 +24076,7 @@
         <f>B155</f>
         <v/>
       </c>
-      <c r="H155" t="n">
+      <c r="H155" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I155" s="0">
@@ -24103,7 +24103,7 @@
         <f>B156</f>
         <v/>
       </c>
-      <c r="H156" t="n">
+      <c r="H156" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I156" s="0">
@@ -24130,7 +24130,7 @@
         <f>B157</f>
         <v/>
       </c>
-      <c r="H157" t="n">
+      <c r="H157" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I157" s="0">
@@ -24157,7 +24157,7 @@
         <f>B158</f>
         <v/>
       </c>
-      <c r="H158" t="n">
+      <c r="H158" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I158" s="0">
@@ -24184,7 +24184,7 @@
         <f>B159</f>
         <v/>
       </c>
-      <c r="H159" t="n">
+      <c r="H159" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I159" s="0">
@@ -24211,7 +24211,7 @@
         <f>B160</f>
         <v/>
       </c>
-      <c r="H160" t="n">
+      <c r="H160" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I160" s="0">
@@ -24224,7 +24224,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="H161" t="n">
+      <c r="H161" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I161" s="0">
@@ -24237,7 +24237,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="H162" t="n">
+      <c r="H162" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I162" s="0">
@@ -24250,7 +24250,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="H163" t="n">
+      <c r="H163" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I163" s="0">
@@ -24263,7 +24263,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="H164" t="n">
+      <c r="H164" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I164" s="0">
@@ -24276,7 +24276,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="H165" t="n">
+      <c r="H165" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I165" s="0">
@@ -24289,7 +24289,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="H166" t="n">
+      <c r="H166" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I166" s="0">
@@ -24302,7 +24302,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="H167" t="n">
+      <c r="H167" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I167" s="0">
@@ -24315,7 +24315,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="H168" t="n">
+      <c r="H168" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I168" s="0">
@@ -24328,7 +24328,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="H169" t="n">
+      <c r="H169" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I169" s="0">
@@ -24341,7 +24341,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="H170" t="n">
+      <c r="H170" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I170" s="0">
@@ -24354,7 +24354,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="H171" t="n">
+      <c r="H171" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I171" s="0">
@@ -24367,7 +24367,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="H172" t="n">
+      <c r="H172" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I172" s="0">
@@ -24380,7 +24380,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="H173" t="n">
+      <c r="H173" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I173" s="0">
@@ -24393,7 +24393,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="H174" t="n">
+      <c r="H174" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I174" s="0">
@@ -24406,7 +24406,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="H175" t="n">
+      <c r="H175" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I175" s="0">
@@ -24419,7 +24419,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="H176" t="n">
+      <c r="H176" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I176" s="0">
@@ -24432,7 +24432,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="H177" t="n">
+      <c r="H177" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I177" s="0">
@@ -24445,7 +24445,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="H178" t="n">
+      <c r="H178" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I178" s="0">
@@ -24458,7 +24458,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="H179" t="n">
+      <c r="H179" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I179" s="0">
@@ -24471,7 +24471,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="H180" t="n">
+      <c r="H180" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I180" s="0">
@@ -24484,7 +24484,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="H181" t="n">
+      <c r="H181" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I181" s="0">
@@ -24497,7 +24497,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="H182" t="n">
+      <c r="H182" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I182" s="0">
@@ -24510,7 +24510,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="H183" t="n">
+      <c r="H183" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I183" s="0">
@@ -24523,7 +24523,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="H184" t="n">
+      <c r="H184" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I184" s="0">
@@ -24536,7 +24536,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="H185" t="n">
+      <c r="H185" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I185" s="0">
@@ -24549,7 +24549,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="H186" t="n">
+      <c r="H186" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I186" s="0">
@@ -24562,7 +24562,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="H187" t="n">
+      <c r="H187" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I187" s="0">
@@ -24575,7 +24575,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="H188" t="n">
+      <c r="H188" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I188" s="0">
@@ -24588,7 +24588,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="H189" t="n">
+      <c r="H189" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I189" s="0">
@@ -24601,7 +24601,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="H190" t="n">
+      <c r="H190" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I190" s="0">
@@ -24614,7 +24614,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="H191" t="n">
+      <c r="H191" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I191" s="0">
@@ -24627,7 +24627,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="H192" t="n">
+      <c r="H192" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I192" s="0">
@@ -24640,7 +24640,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="H193" t="n">
+      <c r="H193" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I193" s="0">
@@ -24653,7 +24653,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="H194" t="n">
+      <c r="H194" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I194" s="0">
@@ -24666,7 +24666,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="H195" t="n">
+      <c r="H195" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I195" s="0">
@@ -24679,7 +24679,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="H196" t="n">
+      <c r="H196" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I196" s="0">
@@ -24692,7 +24692,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="H197" t="n">
+      <c r="H197" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I197" s="0">
@@ -24705,7 +24705,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="H198" t="n">
+      <c r="H198" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I198" s="0">
@@ -24718,7 +24718,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="H199" t="n">
+      <c r="H199" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I199" s="0">
@@ -24731,7 +24731,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="H200" t="n">
+      <c r="H200" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I200" s="0">
@@ -24744,7 +24744,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="H201" t="n">
+      <c r="H201" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I201" s="0">
@@ -24757,7 +24757,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="H202" t="n">
+      <c r="H202" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I202" s="0">
@@ -24770,7 +24770,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="H203" t="n">
+      <c r="H203" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I203" s="0">
@@ -24783,7 +24783,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="H204" t="n">
+      <c r="H204" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I204" s="0">
@@ -24796,7 +24796,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="H205" t="n">
+      <c r="H205" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I205" s="0">
@@ -24809,7 +24809,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="H206" t="n">
+      <c r="H206" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I206" s="0">
@@ -24822,7 +24822,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="H207" t="n">
+      <c r="H207" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I207" s="0">
@@ -24835,7 +24835,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="H208" t="n">
+      <c r="H208" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I208" s="0">
@@ -24848,7 +24848,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="H209" t="n">
+      <c r="H209" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I209" s="0">
@@ -24861,7 +24861,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="H210" t="n">
+      <c r="H210" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I210" s="0">
@@ -24874,7 +24874,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="H211" t="n">
+      <c r="H211" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I211" s="0">
@@ -24887,7 +24887,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="H212" t="n">
+      <c r="H212" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I212" s="0">
@@ -24900,7 +24900,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="H213" t="n">
+      <c r="H213" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I213" s="0">
@@ -24913,7 +24913,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="H214" t="n">
+      <c r="H214" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I214" s="0">
@@ -24926,7 +24926,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="H215" t="n">
+      <c r="H215" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I215" s="0">
@@ -24939,7 +24939,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="H216" t="n">
+      <c r="H216" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I216" s="0">
@@ -24952,7 +24952,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="H217" t="n">
+      <c r="H217" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I217" s="0">
@@ -24965,7 +24965,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="H218" t="n">
+      <c r="H218" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I218" s="0">
@@ -24978,7 +24978,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="H219" t="n">
+      <c r="H219" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I219" s="0">
@@ -24991,7 +24991,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="H220" t="n">
+      <c r="H220" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I220" s="0">
@@ -25004,7 +25004,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="H221" t="n">
+      <c r="H221" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I221" s="0">
@@ -25017,7 +25017,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="H222" t="n">
+      <c r="H222" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I222" s="0">
@@ -25030,7 +25030,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="H223" t="n">
+      <c r="H223" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I223" s="0">
@@ -25043,7 +25043,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="H224" t="n">
+      <c r="H224" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I224" s="0">
@@ -25056,7 +25056,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="H225" t="n">
+      <c r="H225" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I225" s="0">
@@ -25069,7 +25069,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="H226" t="n">
+      <c r="H226" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I226" s="0">
@@ -25082,7 +25082,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="H227" t="n">
+      <c r="H227" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I227" s="0">
@@ -25095,7 +25095,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="H228" t="n">
+      <c r="H228" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I228" s="0">
@@ -25108,7 +25108,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="H229" t="n">
+      <c r="H229" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I229" s="0">
@@ -25121,7 +25121,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="H230" t="n">
+      <c r="H230" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I230" s="0">
@@ -25134,7 +25134,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="H231" t="n">
+      <c r="H231" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I231" s="0">
@@ -25147,7 +25147,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="H232" t="n">
+      <c r="H232" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I232" s="0">
@@ -25160,7 +25160,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="H233" t="n">
+      <c r="H233" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I233" s="0">
@@ -25173,7 +25173,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="H234" t="n">
+      <c r="H234" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I234" s="0">
@@ -25186,7 +25186,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="H235" t="n">
+      <c r="H235" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I235" s="0">
@@ -25199,7 +25199,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="H236" t="n">
+      <c r="H236" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I236" s="0">
@@ -25212,7 +25212,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="H237" t="n">
+      <c r="H237" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I237" s="0">
@@ -25225,7 +25225,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="H238" t="n">
+      <c r="H238" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I238" s="0">
@@ -25238,7 +25238,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="H239" t="n">
+      <c r="H239" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I239" s="0">
@@ -25251,7 +25251,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="H240" t="n">
+      <c r="H240" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I240" s="0">
@@ -25264,7 +25264,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="H241" t="n">
+      <c r="H241" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I241" s="0">
@@ -25277,7 +25277,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="H242" t="n">
+      <c r="H242" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I242" s="0">
@@ -25290,7 +25290,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="H243" t="n">
+      <c r="H243" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I243" s="0">
@@ -25303,7 +25303,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="H244" t="n">
+      <c r="H244" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I244" s="0">
@@ -25316,7 +25316,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="H245" t="n">
+      <c r="H245" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I245" s="0">
@@ -25329,7 +25329,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="H246" t="n">
+      <c r="H246" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I246" s="0">
@@ -25342,7 +25342,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="H247" t="n">
+      <c r="H247" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I247" s="0">
@@ -25355,7 +25355,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="H248" t="n">
+      <c r="H248" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I248" s="0">
@@ -25368,7 +25368,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="H249" t="n">
+      <c r="H249" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I249" s="0">
@@ -25381,7 +25381,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="H250" t="n">
+      <c r="H250" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I250" s="0">
@@ -25394,7 +25394,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="H251" t="n">
+      <c r="H251" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I251" s="0">
@@ -25407,7 +25407,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="H252" t="n">
+      <c r="H252" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I252" s="0">
@@ -25420,7 +25420,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="H253" t="n">
+      <c r="H253" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I253" s="0">
@@ -25433,7 +25433,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="H254" t="n">
+      <c r="H254" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I254" s="0">
@@ -25446,7 +25446,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="H255" t="n">
+      <c r="H255" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I255" s="0">
@@ -25459,7 +25459,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="H256" t="n">
+      <c r="H256" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I256" s="0">
@@ -25472,7 +25472,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="H257" t="n">
+      <c r="H257" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I257" s="0">
@@ -25485,7 +25485,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="H258" t="n">
+      <c r="H258" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I258" s="0">
@@ -25498,7 +25498,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="H259" t="n">
+      <c r="H259" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I259" s="0">
@@ -25511,7 +25511,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="H260" t="n">
+      <c r="H260" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I260" s="0">
@@ -25524,7 +25524,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="H261" t="n">
+      <c r="H261" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I261" s="0">
@@ -25537,7 +25537,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="H262" t="n">
+      <c r="H262" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I262" s="0">
@@ -25550,7 +25550,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="H263" t="n">
+      <c r="H263" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I263" s="0">
@@ -25563,7 +25563,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="H264" t="n">
+      <c r="H264" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I264" s="0">
@@ -25576,7 +25576,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="H265" t="n">
+      <c r="H265" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I265" s="0">
@@ -25589,7 +25589,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="H266" t="n">
+      <c r="H266" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I266" s="0">
@@ -25602,7 +25602,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="H267" t="n">
+      <c r="H267" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I267" s="0">
@@ -25615,7 +25615,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="H268" t="n">
+      <c r="H268" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I268" s="0">
@@ -25628,7 +25628,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="H269" t="n">
+      <c r="H269" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I269" s="0">
@@ -25641,7 +25641,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="H270" t="n">
+      <c r="H270" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I270" s="0">
@@ -25654,7 +25654,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="H271" t="n">
+      <c r="H271" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I271" s="0">
@@ -25667,7 +25667,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="H272" t="n">
+      <c r="H272" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I272" s="0">
@@ -25680,7 +25680,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="H273" t="n">
+      <c r="H273" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I273" s="0">
@@ -25693,7 +25693,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="H274" t="n">
+      <c r="H274" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I274" s="0">
@@ -25706,7 +25706,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="H275" t="n">
+      <c r="H275" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I275" s="0">
@@ -25719,7 +25719,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="H276" t="n">
+      <c r="H276" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I276" s="0">
@@ -25732,7 +25732,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="H277" t="n">
+      <c r="H277" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I277" s="0">
@@ -25745,7 +25745,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="H278" t="n">
+      <c r="H278" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I278" s="0">
@@ -25758,7 +25758,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="H279" t="n">
+      <c r="H279" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I279" s="0">
@@ -25771,7 +25771,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="H280" t="n">
+      <c r="H280" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I280" s="0">
@@ -25784,7 +25784,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="H281" t="n">
+      <c r="H281" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I281" s="0">
@@ -25797,7 +25797,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="H282" t="n">
+      <c r="H282" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I282" s="0">
@@ -25810,7 +25810,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="H283" t="n">
+      <c r="H283" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I283" s="0">
@@ -25823,7 +25823,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="H284" t="n">
+      <c r="H284" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I284" s="0">
@@ -25836,7 +25836,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="H285" t="n">
+      <c r="H285" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I285" s="0">
@@ -25849,7 +25849,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="H286" t="n">
+      <c r="H286" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I286" s="0">
@@ -25862,7 +25862,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="H287" t="n">
+      <c r="H287" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I287" s="0">
@@ -25875,7 +25875,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="H288" t="n">
+      <c r="H288" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I288" s="0">
@@ -25888,7 +25888,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="H289" t="n">
+      <c r="H289" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I289" s="0">
@@ -25901,7 +25901,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="H290" t="n">
+      <c r="H290" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I290" s="0">
@@ -25914,7 +25914,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="H291" t="n">
+      <c r="H291" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I291" s="0">
@@ -25927,7 +25927,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="H292" t="n">
+      <c r="H292" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I292" s="0">
@@ -25940,7 +25940,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="H293" t="n">
+      <c r="H293" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I293" s="0">
@@ -25953,7 +25953,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="H294" t="n">
+      <c r="H294" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I294" s="0">
@@ -25966,7 +25966,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="H295" t="n">
+      <c r="H295" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I295" s="0">
@@ -25979,7 +25979,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="H296" t="n">
+      <c r="H296" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I296" s="0">
@@ -25992,7 +25992,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="H297" t="n">
+      <c r="H297" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I297" s="0">
@@ -26005,7 +26005,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="H298" t="n">
+      <c r="H298" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I298" s="0">
@@ -26018,7 +26018,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="H299" t="n">
+      <c r="H299" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I299" s="0">
@@ -26031,7 +26031,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="H300" t="n">
+      <c r="H300" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I300" s="0">
@@ -26044,7 +26044,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="H301" t="n">
+      <c r="H301" s="0" t="n">
         <v>0.018</v>
       </c>
       <c r="I301" s="0">
